--- a/files/港岛-湾仔-坚尼地道33号.xlsx
+++ b/files/港岛-湾仔-坚尼地道33号.xlsx
@@ -603,7 +603,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
@@ -699,7 +699,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -4071,7 +4071,7 @@
           <t>SOUTH | 1562呎 (3房)
 $7,810万
 $50,000/呎
-(26年-06月)</t>
+(已售)</t>
         </is>
       </c>
     </row>
